--- a/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v2_qwen_7b_dataset_comparison.xlsx
+++ b/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v2_qwen_7b_dataset_comparison.xlsx
@@ -568,23 +568,23 @@
   <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v2_qwen_7b_dataset_comparison.xlsx
+++ b/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v2_qwen_7b_dataset_comparison.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,11 @@
       <b val="1"/>
     </font>
     <font/>
+    <font>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -49,12 +52,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
-        <bgColor rgb="00BDD7EE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -173,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -184,20 +181,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1113,7 +1104,7 @@
       <c r="M9" s="5" t="n">
         <v>0.8929219390813675</v>
       </c>
-      <c r="N9" s="10" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1124,7 +1115,7 @@
       <c r="P9" s="5" t="n">
         <v>0.7718260869565234</v>
       </c>
-      <c r="Q9" s="10" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1165,7 +1156,7 @@
       <c r="J10" s="5" t="n">
         <v>74.69429347826086</v>
       </c>
-      <c r="K10" s="10" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1176,7 +1167,7 @@
       <c r="M10" s="5" t="n">
         <v>0.834988152817287</v>
       </c>
-      <c r="N10" s="10" t="inlineStr">
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1187,7 +1178,7 @@
       <c r="P10" s="5" t="n">
         <v>0.6513735485698117</v>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1228,7 +1219,7 @@
       <c r="J11" s="8" t="n">
         <v>88.75579598145286</v>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1239,7 +1230,7 @@
       <c r="M11" s="8" t="n">
         <v>0.8882304176573891</v>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1250,7 +1241,7 @@
       <c r="P11" s="8" t="n">
         <v>0.7560975609756128</v>
       </c>
-      <c r="Q11" s="11" t="inlineStr">
+      <c r="Q11" s="9" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>

--- a/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v2_qwen_7b_dataset_comparison.xlsx
+++ b/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v2_qwen_7b_dataset_comparison.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,10 +30,13 @@
     </font>
     <font/>
     <font>
+      <color rgb="009C6500"/>
+    </font>
+    <font>
       <color rgb="00006100"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +47,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
         <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -170,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -184,11 +193,14 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -723,7 +735,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>dev_v2</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
@@ -732,7 +744,7 @@
       <c r="G3" s="5" t="n">
         <v>60.33828420056634</v>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -760,7 +772,7 @@
       <c r="Q3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n"/>
+      <c r="A4" s="8" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
           <t>enru</t>
@@ -772,7 +784,7 @@
       <c r="D4" s="5" t="n">
         <v>24.68482631500832</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -783,7 +795,7 @@
       <c r="G4" s="5" t="n">
         <v>54.37295469501902</v>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -812,54 +824,54 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n"/>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>enes</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="9" t="n">
         <v>42.70958403092523</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="9" t="n">
         <v>44.66703003757013</v>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>dev_v2</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n">
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>dev_v2</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>66.17691643590605</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="9" t="n">
         <v>67.43058465313958</v>
       </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>dev_v2</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="K5" s="8" t="n"/>
-      <c r="L5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="8" t="n"/>
-      <c r="O5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="8" t="n"/>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>dev_v2</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -878,7 +890,7 @@
       <c r="D6" s="5" t="n">
         <v>38.643176271946</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -889,7 +901,7 @@
       <c r="G6" s="5" t="n">
         <v>68.26380076747647</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -900,7 +912,7 @@
       <c r="J6" s="5" t="n">
         <v>80.3369341563786</v>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -911,7 +923,7 @@
       <c r="M6" s="5" t="n">
         <v>0.952332749063073</v>
       </c>
-      <c r="N6" s="6" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -922,14 +934,14 @@
       <c r="P6" s="5" t="n">
         <v>0.87037037037037</v>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
+      <c r="A7" s="8" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
           <t>enru</t>
@@ -941,7 +953,7 @@
       <c r="D7" s="5" t="n">
         <v>35.39755152380427</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -952,7 +964,7 @@
       <c r="G7" s="5" t="n">
         <v>64.19875698084608</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -963,7 +975,7 @@
       <c r="J7" s="5" t="n">
         <v>76.54554630330558</v>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -974,7 +986,7 @@
       <c r="M7" s="5" t="n">
         <v>0.9230803600557814</v>
       </c>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -985,7 +997,7 @@
       <c r="P7" s="5" t="n">
         <v>0.7693236714975848</v>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -993,62 +1005,62 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n"/>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>enes</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="9" t="n">
         <v>47.8942358280286</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="9" t="n">
         <v>54.69569022959442</v>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>dev_v2</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>dev_v2</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
         <v>71.65589605978859</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="9" t="n">
         <v>75.16285839427655</v>
       </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>dev_v2</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="n">
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>dev_v2</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
         <v>84.6820809248555</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="J8" s="9" t="n">
         <v>93.23809523809523</v>
       </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>dev_v2</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="n">
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>dev_v2</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="n">
         <v>0.9071166827178107</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="9" t="n">
         <v>0.9666112022279311</v>
       </c>
-      <c r="N8" s="9" t="inlineStr">
-        <is>
-          <t>dev_v2</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="n">
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>dev_v2</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="n">
         <v>0.8023255813953492</v>
       </c>
-      <c r="P8" s="8" t="n">
+      <c r="P8" s="9" t="n">
         <v>0.8778018799710753</v>
       </c>
-      <c r="Q8" s="9" t="inlineStr">
+      <c r="Q8" s="10" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -1071,7 +1083,7 @@
       <c r="D9" s="5" t="n">
         <v>34.42323375222445</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -1082,7 +1094,7 @@
       <c r="G9" s="5" t="n">
         <v>63.92015107311587</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -1093,7 +1105,7 @@
       <c r="J9" s="5" t="n">
         <v>79.89303266840128</v>
       </c>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -1104,7 +1116,7 @@
       <c r="M9" s="5" t="n">
         <v>0.8929219390813675</v>
       </c>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1115,14 +1127,14 @@
       <c r="P9" s="5" t="n">
         <v>0.7718260869565234</v>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="7" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n"/>
+      <c r="A10" s="8" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
           <t>enru</t>
@@ -1134,7 +1146,7 @@
       <c r="D10" s="5" t="n">
         <v>29.50320367768739</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -1145,7 +1157,7 @@
       <c r="G10" s="5" t="n">
         <v>59.52284986795837</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>dev_v2</t>
         </is>
@@ -1156,7 +1168,7 @@
       <c r="J10" s="5" t="n">
         <v>74.69429347826086</v>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1167,7 +1179,7 @@
       <c r="M10" s="5" t="n">
         <v>0.834988152817287</v>
       </c>
-      <c r="N10" s="6" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1178,7 +1190,7 @@
       <c r="P10" s="5" t="n">
         <v>0.6513735485698117</v>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="7" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1186,62 +1198,62 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>enes</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <v>44.18766571500803</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="9" t="n">
         <v>47.97280217248825</v>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>dev_v2</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>dev_v2</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
         <v>67.90462308500811</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="9" t="n">
         <v>70.88348427463508</v>
       </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>dev_v2</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="n">
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>dev_v2</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="n">
         <v>93.29113924050633</v>
       </c>
-      <c r="J11" s="8" t="n">
+      <c r="J11" s="9" t="n">
         <v>88.75579598145286</v>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="L11" s="9" t="n">
         <v>0.9567446618079528</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.8882304176573891</v>
       </c>
-      <c r="N11" s="9" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
       </c>
-      <c r="O11" s="8" t="n">
+      <c r="O11" s="9" t="n">
         <v>0.9054545454545455</v>
       </c>
-      <c r="P11" s="8" t="n">
+      <c r="P11" s="9" t="n">
         <v>0.7560975609756128</v>
       </c>
-      <c r="Q11" s="9" t="inlineStr">
+      <c r="Q11" s="10" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
